--- a/02_Dataset/data dictionary.xlsx
+++ b/02_Dataset/data dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ac6732527afc1fc/Documents/churn dataset/data dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{552BB324-3708-48C7-8AFF-A4C935F52ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B10033A-BC95-453B-9A19-00A88528A741}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{552BB324-3708-48C7-8AFF-A4C935F52ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B38144D2-C189-4F5B-BFEC-74BD8556F69B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ABCC6E63-0C85-4E42-88A2-5E2F4A4BAABF}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
     <sheet name="Products" sheetId="2" r:id="rId2"/>
     <sheet name="Orders" sheetId="4" r:id="rId3"/>
-    <sheet name="Montly_revenue" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="121">
   <si>
     <t>Column Name</t>
   </si>
@@ -392,52 +391,16 @@
     <t>Indicates whether the customer is a repeat customer (1 = Yes, 0 = No).</t>
   </si>
   <si>
-    <t>Calendar year for the sales summary.</t>
-  </si>
-  <si>
-    <t>Month of the year (1–12) for the sales summary.</t>
-  </si>
-  <si>
-    <t>Fiscal quarter corresponding to the month (Q1, Q2, Q3, Q4).</t>
-  </si>
-  <si>
-    <t>orders</t>
-  </si>
-  <si>
-    <t>Total number of orders placed during the month.</t>
-  </si>
-  <si>
-    <t>revenue_usd</t>
-  </si>
-  <si>
-    <t>Total revenue generated during the month in USD.</t>
-  </si>
-  <si>
-    <t>avg_order_value</t>
-  </si>
-  <si>
-    <t>Average value of each order during the month in USD.</t>
-  </si>
-  <si>
-    <t>Average discount percentage applied to orders during the month.</t>
-  </si>
-  <si>
-    <t>Percentage of orders that were returned during the month.</t>
-  </si>
-  <si>
-    <t>unique_customers</t>
-  </si>
-  <si>
-    <t>Number of distinct customers who placed orders during the month.</t>
-  </si>
-  <si>
-    <t>new_customers</t>
-  </si>
-  <si>
-    <t>Number of customers who made their first purchase during the month.</t>
-  </si>
-  <si>
     <t>Total amount before discounts, taxes, and shipping (Unit Price × Quantity).</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>Unique identifier of the product who placed the order (Foreign Key to Product table).</t>
+  </si>
+  <si>
+    <t>Unique identifier of the product.</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8424ACC8-C12E-4A59-AA7E-4734093E305B}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -1095,101 +1058,112 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>48</v>
+      <c r="A2" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1200,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3FCFCCD-94F2-4008-B4FB-D8D535C5CAAF}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -1243,424 +1217,299 @@
     </row>
     <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>116</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50305F93-7D86-403B-88C6-437C89C4531B}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
